--- a/plots/parse1/data/n_shot_mean_results.xlsx
+++ b/plots/parse1/data/n_shot_mean_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,111 +557,148 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>4_shot</t>
+          <t>3_shot</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50.90654476578604</v>
+        <v>48.76049048313893</v>
       </c>
       <c r="C4" t="n">
-        <v>69.03879713046381</v>
+        <v>69.68734706929152</v>
       </c>
       <c r="D4" t="n">
-        <v>55.74498882334408</v>
+        <v>54.13869077842922</v>
       </c>
       <c r="E4" t="n">
-        <v>1.483357015928692</v>
+        <v>1.61491718354847</v>
       </c>
       <c r="F4" t="n">
-        <v>3.087549485385422</v>
+        <v>2.664760498897369</v>
       </c>
       <c r="G4" t="n">
-        <v>1.606530978611799</v>
+        <v>1.721367881920971</v>
       </c>
       <c r="H4" t="n">
-        <v>5.298908701305947</v>
+        <v>5.782267717028962</v>
       </c>
       <c r="I4" t="n">
-        <v>1.669773842300583</v>
+        <v>2.037437288485185</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5064376558887635</v>
+        <v>0.7028663668572991</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3851284600713081</v>
+        <v>0.4826449480802353</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>5_shot</t>
+          <t>4_shot</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50.82344092562398</v>
+        <v>50.90654476578604</v>
       </c>
       <c r="C5" t="n">
-        <v>67.66714353242131</v>
+        <v>69.03879713046381</v>
       </c>
       <c r="D5" t="n">
-        <v>55.4153471846226</v>
+        <v>55.74498882334408</v>
       </c>
       <c r="E5" t="n">
-        <v>1.648532927561087</v>
+        <v>1.483357015928692</v>
       </c>
       <c r="F5" t="n">
-        <v>3.598796185986185</v>
+        <v>3.087549485385422</v>
       </c>
       <c r="G5" t="n">
-        <v>2.135185969036492</v>
+        <v>1.606530978611799</v>
       </c>
       <c r="H5" t="n">
-        <v>5.16138724861453</v>
+        <v>5.298908701305947</v>
       </c>
       <c r="I5" t="n">
-        <v>1.578034861035499</v>
+        <v>1.669773842300583</v>
       </c>
       <c r="J5" t="n">
-        <v>0.625587842537411</v>
+        <v>0.5064376558887635</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3501108668584431</v>
+        <v>0.3851284600713081</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
+          <t>5_shot</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>50.82344092562398</v>
+      </c>
+      <c r="C6" t="n">
+        <v>67.66714353242131</v>
+      </c>
+      <c r="D6" t="n">
+        <v>55.4153471846226</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.648532927561087</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3.598796185986185</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.135185969036492</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5.16138724861453</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.578034861035499</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.625587842537411</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.3501108668584431</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
           <t>5_shot_best</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
         <v>49.13747491333698</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C7" t="n">
         <v>73.75105661216772</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D7" t="n">
         <v>55.79956151351191</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E7" t="n">
         <v>0</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F7" t="n">
         <v>0</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H7" t="n">
         <v>4.4644481715307</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I7" t="n">
         <v>2.046537864800949</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J7" t="n">
         <v>0</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K7" t="n">
         <v>0</v>
       </c>
     </row>

--- a/plots/parse1/data/n_shot_mean_results.xlsx
+++ b/plots/parse1/data/n_shot_mean_results.xlsx
@@ -672,34 +672,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>49.13747491333698</v>
+        <v>48.69575636668854</v>
       </c>
       <c r="C7" t="n">
-        <v>73.75105661216772</v>
+        <v>70.28557307307308</v>
       </c>
       <c r="D7" t="n">
-        <v>55.79956151351191</v>
+        <v>54.34533187281981</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.5901270855090935</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2.457367945268278</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1.205345273510584</v>
       </c>
       <c r="H7" t="n">
-        <v>4.4644481715307</v>
+        <v>5.351211336362317</v>
       </c>
       <c r="I7" t="n">
-        <v>2.046537864800949</v>
+        <v>3.17500142450903</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.5208860804925322</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1.498570312021684</v>
       </c>
     </row>
   </sheetData>

--- a/plots/parse1/data/n_shot_mean_results.xlsx
+++ b/plots/parse1/data/n_shot_mean_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -668,38 +668,112 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
+          <t>5_shot_min</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>47.50789746876737</v>
+      </c>
+      <c r="C7" t="n">
+        <v>65.35204649093539</v>
+      </c>
+      <c r="D7" t="n">
+        <v>51.91323232670088</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.669997587317815</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.282848725792126</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8620353309026333</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5.336477240415784</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.56573568442346</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.2206025908866121</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.2733266885401067</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
           <t>5_shot_best</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B8" t="n">
         <v>48.69575636668854</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C8" t="n">
         <v>70.28557307307308</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D8" t="n">
         <v>54.34533187281981</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E8" t="n">
         <v>0.5901270855090935</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F8" t="n">
         <v>2.457367945268278</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G8" t="n">
         <v>1.205345273510584</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H8" t="n">
         <v>5.351211336362317</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I8" t="n">
         <v>3.17500142450903</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J8" t="n">
         <v>0.5208860804925322</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K8" t="n">
         <v>1.498570312021684</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>5_shot_max</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>49.88126586441683</v>
+      </c>
+      <c r="C9" t="n">
+        <v>75.27430277499721</v>
+      </c>
+      <c r="D9" t="n">
+        <v>56.32204944677939</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.225904135458738</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.392212277438636</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.101294517017501</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5.382674827312965</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.285722715165248</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.3273345486925991</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.2375014025363119</v>
       </c>
     </row>
   </sheetData>
